--- a/src/test/resources/testData/organisation/stf/stf_organisation_error_template.xlsx
+++ b/src/test/resources/testData/organisation/stf/stf_organisation_error_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karthik.jaladurgam/Desktop/STOS/Test data/Business/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karthik.jaladurgam/workspace/securities-transfer-charge-submissions-ui-tests/src/test/resources/testData/organisation/stf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039E9349-DBB8-8C49-8ACA-B50685FDEE26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400B74B2-588C-164D-9B7F-A32C314EFDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
   <si>
     <t xml:space="preserve">Complete one line in this template per transfer. 
 Each transfer must be of one type of security, or class of shares.
@@ -61,9 +61,6 @@
     <t>Seller's address - country</t>
   </si>
   <si>
-    <t>Is the business and the seller connected persons?</t>
-  </si>
-  <si>
     <t>Is the business applying for a relief?</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
   <si>
     <t xml:space="preserve">What is the tax rate for this transaction?
 </t>
-  </si>
-  <si>
-    <t>What type of securities are you buying?</t>
   </si>
   <si>
     <t>How many securities are you buying?</t>
@@ -195,9 +189,6 @@
 (Mandatory if shares are the type of security being transfered)</t>
   </si>
   <si>
-    <t>For example; shares (include the share type), interests in underlying securities, loan notes or other debt securities, or other type of securities.</t>
-  </si>
-  <si>
     <t>Enter an amount in GBP. For example, £600.00 or £193.54.
 Enter the amount of consideration given in exchange for these securities as a cash amount.
 You do not need to provide details about conversion or exchange rates, or how valuations of non-monetary items were made.</t>
@@ -273,7 +264,20 @@
     <t>Seller's name</t>
   </si>
   <si>
-    <t xml:space="preserve">Seller's address - line </t>
+    <t>Seller's address - line 1</t>
+  </si>
+  <si>
+    <t>Are the business and the seller connected persons?</t>
+  </si>
+  <si>
+    <t>What class or type of shares are being transfered?</t>
+  </si>
+  <si>
+    <t>For example ordinary, preference or any other share class or type. 
+(Mandatory if shares are the type of security being bought)</t>
+  </si>
+  <si>
+    <t>If the seller is a business, you must enter the registered business addres</t>
   </si>
 </sst>
 </file>
@@ -315,14 +319,13 @@
     <font>
       <u/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF1155CC"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <u/>
       <sz val="12"/>
-      <color rgb="FF1155CC"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -347,18 +350,9 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -386,10 +380,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,68 +612,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="N1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="P1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="P1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="S1" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="U1" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="R1" t="s">
-        <v>47</v>
-      </c>
-      <c r="S1" t="s">
-        <v>50</v>
-      </c>
-      <c r="T1" t="s">
-        <v>54</v>
-      </c>
-      <c r="U1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:42" ht="153" x14ac:dyDescent="0.2">
@@ -685,13 +681,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
@@ -709,40 +705,40 @@
         <v>6</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
@@ -768,63 +764,63 @@
     </row>
     <row r="3" spans="1:42" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="G3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="K3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="R3" s="5" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="S3" s="5"/>
       <c r="T3" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V3" s="5"/>
       <c r="W3" s="5"/>
@@ -850,7 +846,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L3" r:id="rId1" xr:uid="{DB00CE6C-DEE5-B543-A592-F96BE8E62787}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
